--- a/qa-test-results-template.xlsx
+++ b/qa-test-results-template.xlsx
@@ -99,6 +99,63 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00595959"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="001F4E78"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00DDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -503,7 +560,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5378,6 +5435,23 @@
     </row>
   </sheetData>
   <autoFilter ref="A7:J156"/>
+  <conditionalFormatting sqref="F8:F156">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>$F8="Passed"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>$F8="Fail" OR $F8="Failed"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
+      <formula>$F8="Not Run"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="0">
+      <formula>$F8="Blocked" OR $F8="Retest"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="4" stopIfTrue="0">
+      <formula>$F8="Skipped"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="F8:F156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Passed,Failed,Blocked,Retest,Skipped,Not Run"</formula1>

--- a/qa-test-results-template.xlsx
+++ b/qa-test-results-template.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cara Pakai" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hasil Run'!$A$7:$J$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hasil Run'!$A$7:$J$159</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J170"/>
+  <dimension ref="A1:J173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5212,29 +5212,21 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>TC-CFL-01</t>
+          <t>RG-20</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Arus Kas</t>
+          <t>Skenario Regresi</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>3 seksi arus kas</t>
-        </is>
-      </c>
-      <c r="D154" s="4" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
+          <t>SESSION_EXPIRED — refresh token kedaluwarsa di server</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr"/>
+      <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="3" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr"/>
@@ -5244,29 +5236,21 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>TC-CFL-02</t>
+          <t>RG-21</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Arus Kas</t>
+          <t>Skenario Regresi</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>Konsistensi kas</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
+          <t>RATE_LIMITED — retry otomatis pulih</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr"/>
+      <c r="E155" s="2" t="inlineStr"/>
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="3" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr"/>
@@ -5276,166 +5260,254 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>TC-CFL-03</t>
+          <t>RG-22</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Arus Kas</t>
+          <t>Skenario Regresi</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Mapping grup akun</t>
-        </is>
-      </c>
-      <c r="D156" s="5" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
+          <t>RATE_LIMITED — tetap diblokir</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr"/>
+      <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="3" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr"/>
       <c r="I156" s="2" t="inlineStr"/>
       <c r="J156" s="2" t="inlineStr"/>
     </row>
-    <row r="157"/>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>TC-CFL-01</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Arus Kas</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>3 seksi arus kas</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr"/>
+      <c r="G157" s="3" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr"/>
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+    </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>RINGKASAN RUN</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr"/>
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>TC-CFL-02</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Arus Kas</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Konsistensi kas</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr"/>
+      <c r="G158" s="3" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr"/>
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Passed</t>
-        </is>
-      </c>
-      <c r="B159">
-        <f>COUNTIF(F8:F156,"Passed")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Failed</t>
-        </is>
-      </c>
-      <c r="B160">
-        <f>COUNTIF(F8:F156,"Failed")</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>TC-CFL-03</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Arus Kas</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>Mapping grup akun</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr"/>
+      <c r="G159" s="3" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr"/>
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160"/>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Blocked</t>
-        </is>
-      </c>
-      <c r="B161">
-        <f>COUNTIF(F8:F156,"Blocked")</f>
-        <v/>
-      </c>
+          <t>RINGKASAN RUN</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Retest</t>
+          <t xml:space="preserve">  Passed</t>
         </is>
       </c>
       <c r="B162">
-        <f>COUNTIF(F8:F156,"Retest")</f>
+        <f>COUNTIF(F8:F159,"Passed")</f>
         <v/>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Skipped</t>
+          <t xml:space="preserve">  Failed</t>
         </is>
       </c>
       <c r="B163">
-        <f>COUNTIF(F8:F156,"Skipped")</f>
+        <f>COUNTIF(F8:F159,"Failed")</f>
         <v/>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Not Run</t>
+          <t xml:space="preserve">  Blocked</t>
         </is>
       </c>
       <c r="B164">
-        <f>COUNTIF(F8:F156,"Not Run")</f>
+        <f>COUNTIF(F8:F159,"Blocked")</f>
         <v/>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total dijalankan (bukan Not Run)</t>
+          <t xml:space="preserve">  Retest</t>
         </is>
       </c>
       <c r="B165">
-        <f>COUNTA(F8:F156)-COUNTIF(F8:F156,"Not Run")-COUNTIF(F8:F156,"")</f>
+        <f>COUNTIF(F8:F159,"Retest")</f>
         <v/>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">  % Pass</t>
+          <t xml:space="preserve">  Skipped</t>
         </is>
       </c>
       <c r="B166">
-        <f>IF(COUNTA(F8:F156)=0,0,COUNTIF(F8:F156,"Passed")/COUNTA(F8:F156))</f>
+        <f>COUNTIF(F8:F159,"Skipped")</f>
         <v/>
       </c>
     </row>
-    <row r="167"/>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Not Run</t>
+        </is>
+      </c>
+      <c r="B167">
+        <f>COUNTIF(F8:F159,"Not Run")</f>
+        <v/>
+      </c>
+    </row>
     <row r="168">
-      <c r="A168" s="6" t="inlineStr">
-        <is>
-          <t>RELEASE GATE (S1)</t>
-        </is>
-      </c>
-      <c r="B168" s="6" t="inlineStr"/>
+      <c r="A168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total dijalankan (bukan Not Run)</t>
+        </is>
+      </c>
+      <c r="B168">
+        <f>COUNTA(F8:F159)-COUNTIF(F8:F159,"Not Run")-COUNTIF(F8:F159,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
+          <t xml:space="preserve">  % Pass</t>
+        </is>
+      </c>
+      <c r="B169">
+        <f>IF(COUNTA(F8:F159)=0,0,COUNTIF(F8:F159,"Passed")/COUNTA(F8:F159))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170"/>
+    <row r="171">
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t>RELEASE GATE (S1)</t>
+        </is>
+      </c>
+      <c r="B171" s="6" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
           <t xml:space="preserve">  S1 belum lolos (Failed/Not Run)</t>
         </is>
       </c>
-      <c r="B169">
-        <f>COUNTIFS(D8:D156,"S1",F8:F156,"&lt;&gt;Passed")-COUNTIFS(D8:D156,"S1",F8:F156,"",F8:F156,"&lt;&gt;")</f>
+      <c r="B172">
+        <f>COUNTIFS(D8:D159,"S1",F8:F159,"&lt;&gt;Passed")-COUNTIFS(D8:D159,"S1",F8:F159,"",F8:F159,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
+    <row r="173">
+      <c r="A173" t="inlineStr">
         <is>
           <t xml:space="preserve">  Blokir rilis jika S1 belum lolos</t>
         </is>
       </c>
-      <c r="B170">
-        <f>IF(COUNTIFS(D8:D156,"S1",F8:F156,"&lt;&gt;Passed")&gt;0,"YA — selesaikan S1 dulu","TIDAK")</f>
+      <c r="B173">
+        <f>IF(COUNTIFS(D8:D159,"S1",F8:F159,"&lt;&gt;Passed")&gt;0,"YA — selesaikan S1 dulu","TIDAK")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:J156"/>
-  <conditionalFormatting sqref="F8:F156">
+  <autoFilter ref="A7:J159"/>
+  <conditionalFormatting sqref="F8:F159">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$F8="Passed"</formula>
     </cfRule>
@@ -5453,7 +5525,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F8:F156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F8:F159" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Passed,Failed,Blocked,Retest,Skipped,Not Run"</formula1>
     </dataValidation>
   </dataValidations>

--- a/qa-test-results-template.xlsx
+++ b/qa-test-results-template.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
